--- a/examples/jpetstore-6/.understand-anything/doc-output/si-인터페이스정의서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-인터페이스정의서.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="API 목록" sheetId="1" r:id="rId1"/>
-    <sheet name="대외 연계(송신·라우트 외 수신)" sheetId="2" r:id="rId2"/>
+    <sheet name="문서정보" sheetId="1" r:id="rId1"/>
+    <sheet name="API 목록" sheetId="2" r:id="rId2"/>
+    <sheet name="대외 연계(송신·라우트 외 수신)" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +59,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>문서명</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SI 인터페이스정의서</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>방법론</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>si-standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>소스 커밋</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[미확인]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>작성자 / 버전 / 작성일</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[미확인] — 제출 전 사람이 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>본 파일의 지위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>정적 스캔 스냅샷(원천 데이터) — 대시보드에서의 확정 편집은 반영되지 않음. 최신화는 /understand-docs 재실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>신뢰도 표기</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[확정]=정적 분석 근거(file:line) 보유, [추정]=추론, [미확인]=사람 채움 대상 — 사람 검수/사인오프 여부와 무관.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
@@ -1151,10 +1248,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I23"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-인터페이스정의서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-인터페이스정의서.xlsx
@@ -107,7 +107,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
